--- a/KatalonData/EmailTextToPay/ManualEntry_Demo.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry_Demo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{07CC7C08-9196-4BAE-BEDA-C249FE0EB02C}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{DA81A108-847B-4A49-8D1E-5B6995BEB77B}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
     <workbookView activeTab="1" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="104">
   <si>
     <t>Result</t>
   </si>
@@ -228,60 +228,6 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Fri Mar 13 20:49:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Mar 13 20:52:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Mar 13 20:53:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Mar 13 20:54:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 18 01:22:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 18 01:22:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 18 01:49:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 18 01:50:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 18 01:50:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 18 01:51:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 18 01:51:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 18 01:52:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 18 01:52:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 18 01:53:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 18 01:53:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:24:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:25:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:44:13 IST 2026</t>
-  </si>
-  <si>
     <t>UDF1</t>
   </si>
   <si>
@@ -291,67 +237,118 @@
     <t>UDF3</t>
   </si>
   <si>
-    <t>Wed Mar 25 15:48:05 IST 2026</t>
+    <t>Wed Mar 25 18:26:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:27:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:27:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:28:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:28:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:29:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:29:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:30:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:30:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:31:27 IST 2026</t>
+  </si>
+  <si>
+    <t>DueDate</t>
+  </si>
+  <si>
+    <t>Payment app+Mandatory+nonMandatory+email+phone+Due Date</t>
+  </si>
+  <si>
+    <t>Payment app+Mandatory+nonMandatory+email+phone+ no Due Date</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 20:45:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 20:46:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 20:47:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 20:48:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 20:50:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 20:51:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 20:52:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 20:53:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 20:54:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 20:55:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 20:56:42 IST 2026</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Wed Mar 25 18:20:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:21:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:21:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:22:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:23:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:23:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:24:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:25:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:25:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:26:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:27:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:27:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:28:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:28:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:29:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:29:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:30:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:30:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:31:27 IST 2026</t>
+    <t>Thu Jun 18 21:03:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 21:05:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 21:06:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 21:06:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 21:07:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 21:08:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 21:09:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 21:10:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 21:10:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 21:11:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 21:12:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 21:13:18 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -889,7 +886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="6.26953125" collapsed="true"/>
@@ -903,16 +900,17 @@
     <col min="10" max="10" customWidth="true" style="6" width="17.7265625" collapsed="true"/>
     <col min="11" max="11" customWidth="true" style="6" width="11.90625" collapsed="true"/>
     <col min="12" max="12" customWidth="true" style="6" width="15.0" collapsed="true"/>
-    <col min="13" max="14" customWidth="true" style="6" width="14.453125" collapsed="true"/>
-    <col min="15" max="15" customWidth="true" style="6" width="7.81640625" collapsed="true"/>
-    <col min="16" max="16" customWidth="true" style="6" width="9.1796875" collapsed="true"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="6" width="13.90625" collapsed="true"/>
-    <col min="18" max="18" customWidth="true" style="6" width="11.81640625" collapsed="true"/>
-    <col min="19" max="27" style="6" width="8.7265625" collapsed="true"/>
-    <col min="28" max="16384" style="1" width="8.7265625" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="6" width="11.453125" collapsed="true"/>
+    <col min="14" max="15" customWidth="true" style="6" width="14.453125" collapsed="true"/>
+    <col min="16" max="16" customWidth="true" style="6" width="7.81640625" collapsed="true"/>
+    <col min="17" max="17" customWidth="true" style="6" width="9.1796875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="6" width="13.90625" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="6" width="11.81640625" collapsed="true"/>
+    <col min="20" max="28" style="6" width="8.7265625" collapsed="true"/>
+    <col min="29" max="16384" style="1" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" ht="25" r="1" s="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row customFormat="1" ht="25" r="1" s="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -950,57 +948,60 @@
         <v>17</v>
       </c>
       <c r="M1" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="N1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="O1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="P1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="Q1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="18" t="s">
+      <c r="R1" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="14" t="s">
-        <v>81</v>
-      </c>
       <c r="S1" s="14" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="T1" s="14" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="U1" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="V1" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="14" t="s">
+      <c r="W1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="14" t="s">
+      <c r="X1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="14" t="s">
+      <c r="Y1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="14" t="s">
+      <c r="Z1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="14" t="s">
+      <c r="AA1" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" s="14" t="s">
+      <c r="AB1" s="14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row customFormat="1" customHeight="1" ht="19" r="2" s="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row customFormat="1" customHeight="1" ht="19" r="2" s="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>50</v>
@@ -1032,20 +1033,21 @@
       <c r="R2" s="8"/>
       <c r="S2" s="8"/>
       <c r="T2" s="8"/>
-      <c r="U2" s="9"/>
+      <c r="U2" s="8"/>
       <c r="V2" s="9"/>
       <c r="W2" s="9"/>
       <c r="X2" s="9"/>
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
       <c r="AA2" s="9"/>
-    </row>
-    <row customHeight="1" ht="21.5" r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB2" s="9"/>
+    </row>
+    <row customHeight="1" ht="21.5" r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>51</v>
@@ -1067,12 +1069,12 @@
         <v>1234567890</v>
       </c>
     </row>
-    <row ht="25" r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row ht="25" r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>52</v>
@@ -1096,12 +1098,12 @@
         <v>1234567890</v>
       </c>
     </row>
-    <row customHeight="1" ht="38" r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row customHeight="1" ht="38" r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>62</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>55</v>
@@ -1124,37 +1126,37 @@
       <c r="L5" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="N5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="O5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="P5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="P5" s="6">
+      <c r="Q5" s="6">
         <v>123456</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="R5" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R5" s="6" t="s">
+      <c r="S5" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="S5" s="6" t="s">
+      <c r="T5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="T5" s="6" t="s">
+      <c r="U5" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row ht="37.5" r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>62</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>53</v>
@@ -1177,37 +1179,37 @@
       <c r="L6" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="N6" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="O6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="O6" s="6" t="s">
+      <c r="P6" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="P6" s="6">
+      <c r="Q6" s="6">
         <v>123456</v>
       </c>
-      <c r="Q6" s="6" t="s">
+      <c r="R6" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R6" s="6" t="s">
+      <c r="S6" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="S6" s="6" t="s">
+      <c r="T6" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="T6" s="6" t="s">
+      <c r="U6" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row ht="37.5" r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>62</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>54</v>
@@ -1233,37 +1235,37 @@
       <c r="L7" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="N7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="N7" s="6" t="s">
+      <c r="O7" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="O7" s="6" t="s">
+      <c r="P7" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="P7" s="6">
+      <c r="Q7" s="6">
         <v>123456</v>
       </c>
-      <c r="Q7" s="6" t="s">
+      <c r="R7" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R7" s="6" t="s">
+      <c r="S7" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="S7" s="6" t="s">
+      <c r="T7" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="T7" s="6" t="s">
+      <c r="U7" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row ht="37.5" r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C8" s="23" t="s">
         <v>47</v>
@@ -1286,16 +1288,16 @@
       <c r="K8" s="6">
         <v>1234567890</v>
       </c>
-      <c r="P8" s="6">
+      <c r="Q8" s="6">
         <v>22201</v>
       </c>
     </row>
-    <row ht="37.5" r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C9" s="23" t="s">
         <v>48</v>
@@ -1315,16 +1317,16 @@
       <c r="J9" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="P9" s="6">
+      <c r="Q9" s="6">
         <v>22201</v>
       </c>
     </row>
-    <row ht="37.5" r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>62</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C10" s="23" t="s">
         <v>49</v>
@@ -1344,8 +1346,126 @@
       <c r="K10" s="6">
         <v>1234567890</v>
       </c>
-      <c r="P10" s="6">
+      <c r="Q10" s="6">
         <v>22201</v>
+      </c>
+    </row>
+    <row ht="37.5" r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K11" s="6">
+        <v>1234567890</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>123456</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="S11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="T11" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="U11" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row ht="37.5" r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" s="6">
+        <v>1234567890</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>123456</v>
+      </c>
+      <c r="R12" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="S12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="T12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="U12" s="6" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1357,15 +1477,17 @@
     <hyperlink r:id="rId4" ref="J7" xr:uid="{B9848D99-3F02-4B1F-B147-DEC60651F43B}"/>
     <hyperlink r:id="rId5" ref="J8" xr:uid="{FDA63C53-C5A4-429D-B203-33CB3003E9B2}"/>
     <hyperlink r:id="rId6" ref="J9" xr:uid="{4707D785-3286-488B-9C77-6EC977F6DD2D}"/>
+    <hyperlink r:id="rId7" ref="J11" xr:uid="{AFA93351-211A-4D3A-85A8-0471D43A4E7F}"/>
+    <hyperlink r:id="rId8" ref="J12" xr:uid="{ED62CC15-6008-46BC-8F3B-29EB9FFDC4F9}"/>
   </hyperlinks>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="portrait" r:id="rId7"/>
+  <pageSetup orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AD13"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
@@ -1380,23 +1502,24 @@
     <col min="10" max="10" customWidth="true" style="6" width="16.453125" collapsed="true"/>
     <col min="11" max="11" customWidth="true" style="6" width="12.0" collapsed="true"/>
     <col min="12" max="12" customWidth="true" style="6" width="16.0" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="6" width="13.26953125" collapsed="true"/>
-    <col min="14" max="14" customWidth="true" style="6" width="13.453125" collapsed="true"/>
-    <col min="15" max="16" style="6" width="8.7265625" collapsed="true"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="6" width="13.90625" collapsed="true"/>
-    <col min="18" max="18" customWidth="true" style="6" width="11.81640625" collapsed="true"/>
-    <col min="19" max="21" style="6" width="8.7265625" collapsed="true"/>
-    <col min="22" max="22" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
-    <col min="23" max="23" customWidth="true" style="6" width="6.26953125" collapsed="true"/>
-    <col min="24" max="24" customWidth="true" style="6" width="6.0" collapsed="true"/>
-    <col min="25" max="25" customWidth="true" style="6" width="5.90625" collapsed="true"/>
-    <col min="26" max="26" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
-    <col min="27" max="27" customWidth="true" style="6" width="6.54296875" collapsed="true"/>
-    <col min="28" max="28" customWidth="true" style="11" width="47.08984375" collapsed="true"/>
-    <col min="29" max="16384" style="6" width="8.7265625" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="6" width="12.7265625" collapsed="true"/>
+    <col min="14" max="14" customWidth="true" style="6" width="13.26953125" collapsed="true"/>
+    <col min="15" max="15" customWidth="true" style="6" width="13.453125" collapsed="true"/>
+    <col min="16" max="17" style="6" width="8.7265625" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="6" width="13.90625" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="6" width="11.81640625" collapsed="true"/>
+    <col min="20" max="22" style="6" width="8.7265625" collapsed="true"/>
+    <col min="23" max="23" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
+    <col min="24" max="24" customWidth="true" style="6" width="6.26953125" collapsed="true"/>
+    <col min="25" max="25" customWidth="true" style="6" width="6.0" collapsed="true"/>
+    <col min="26" max="26" customWidth="true" style="6" width="5.90625" collapsed="true"/>
+    <col min="27" max="27" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
+    <col min="28" max="28" customWidth="true" style="6" width="6.54296875" collapsed="true"/>
+    <col min="29" max="29" customWidth="true" style="11" width="47.08984375" collapsed="true"/>
+    <col min="30" max="16384" style="6" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1434,60 +1557,63 @@
         <v>17</v>
       </c>
       <c r="M1" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="N1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="O1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="P1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="Q1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="17" t="s">
+      <c r="R1" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="14" t="s">
-        <v>81</v>
-      </c>
       <c r="S1" s="14" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="T1" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="U1" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="U1" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="V1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="15" t="s">
+      <c r="W1" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="15" t="s">
+      <c r="X1" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="15" t="s">
+      <c r="Y1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="15" t="s">
+      <c r="Z1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="15" t="s">
+      <c r="AA1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" s="15" t="s">
+      <c r="AB1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="13" t="s">
+      <c r="AC1" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row ht="37.5" r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>56</v>
@@ -1501,40 +1627,40 @@
       <c r="L2" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="N2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="O2" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="P2" s="6">
+      <c r="Q2" s="6">
         <v>1000</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="R2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="S2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="T2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="U2" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AB2" s="11" t="s">
+      <c r="AC2" s="11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row ht="13" r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row ht="13" r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>27</v>
@@ -1543,16 +1669,16 @@
         <v>4</v>
       </c>
       <c r="E3" s="12"/>
-      <c r="AB3" s="11" t="s">
+      <c r="AC3" s="11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row ht="13" r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row ht="13" r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>26</v>
@@ -1563,16 +1689,16 @@
       <c r="E4" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="AB4" s="11" t="s">
+      <c r="AC4" s="11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row ht="25" r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row ht="25" r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>62</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>34</v>
@@ -1596,31 +1722,31 @@
       <c r="L5" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="N5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="O5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="P5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="P5" s="6">
+      <c r="Q5" s="6">
         <v>1000</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="R5" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="AB5" s="22" t="s">
+      <c r="AC5" s="22" t="s">
         <v>33</v>
       </c>
     </row>
-    <row ht="25" r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row ht="25" r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>62</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>35</v>
@@ -1641,16 +1767,16 @@
       <c r="K6" s="6">
         <v>1234567890</v>
       </c>
-      <c r="AB6" s="22" t="s">
+      <c r="AC6" s="22" t="s">
         <v>33</v>
       </c>
     </row>
-    <row ht="25" r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row ht="25" r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>62</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>37</v>
@@ -1673,16 +1799,16 @@
       <c r="K7" s="6">
         <v>2</v>
       </c>
-      <c r="AB7" s="11" t="s">
+      <c r="AC7" s="11" t="s">
         <v>57</v>
       </c>
     </row>
-    <row ht="25" r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row ht="25" r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>28</v>
@@ -1705,16 +1831,16 @@
       <c r="K8" s="6">
         <v>1234567890</v>
       </c>
-      <c r="AB8" s="11" t="s">
+      <c r="AC8" s="11" t="s">
         <v>58</v>
       </c>
     </row>
-    <row ht="25" r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row ht="25" r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>29</v>
@@ -1731,16 +1857,16 @@
       <c r="I9" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AB9" s="11" t="s">
+      <c r="AC9" s="11" t="s">
         <v>59</v>
       </c>
     </row>
-    <row ht="25" r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row ht="25" r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>62</v>
       </c>
       <c r="B10" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>30</v>
@@ -1760,40 +1886,40 @@
       <c r="L10" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="N10" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="N10" s="6" t="s">
+      <c r="O10" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="O10" s="6" t="s">
+      <c r="P10" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="P10" s="6">
+      <c r="Q10" s="6">
         <v>1000</v>
       </c>
-      <c r="Q10" s="6" t="s">
+      <c r="R10" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="R10" s="6" t="s">
+      <c r="S10" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="S10" s="6" t="s">
+      <c r="T10" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="T10" s="6" t="s">
+      <c r="U10" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AB10" s="11" t="s">
+      <c r="AC10" s="11" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>36</v>
@@ -1804,23 +1930,93 @@
       <c r="L11" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="N11" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="N11" s="6" t="s">
+      <c r="O11" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="O11" s="6" t="s">
+      <c r="P11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="P11" s="6">
+      <c r="Q11" s="6">
         <v>1000</v>
       </c>
-      <c r="Q11" s="6" t="s">
+      <c r="R11" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="AB11" s="11" t="s">
+      <c r="AC11" s="11" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row ht="37.5" r="12" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" s="6">
+        <v>2</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC12" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row ht="37.5" r="13" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J13" s="6">
+        <v>1</v>
+      </c>
+      <c r="K13" s="6">
+        <v>1234567890</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC13" s="11" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1828,8 +2024,9 @@
     <hyperlink r:id="rId1" ref="J5" xr:uid="{588BBDB7-5B95-4FB9-AD9C-36AAC3C41943}"/>
     <hyperlink r:id="rId2" ref="J6" xr:uid="{CE0F2039-EED1-4DB0-83C0-2B84DB370934}"/>
     <hyperlink r:id="rId3" ref="J7" xr:uid="{1B3C72AA-06CB-4051-818C-C62CA26213EB}"/>
+    <hyperlink r:id="rId4" ref="J12" xr:uid="{798B66FB-A2A7-4447-9AB9-4BA6A9BEBA9E}"/>
   </hyperlinks>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
--- a/KatalonData/EmailTextToPay/ManualEntry_Demo.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry_Demo.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="127">
   <si>
     <t>Result</t>
   </si>
@@ -349,6 +349,75 @@
   </si>
   <si>
     <t>Thu Jun 18 21:13:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:46:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:47:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:47:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:48:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:49:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:50:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:51:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:51:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:52:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:53:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:54:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 14:07:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 14:08:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 14:08:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 14:09:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 14:10:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 14:10:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 14:11:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 14:12:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 14:12:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 14:13:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 14:14:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 14:14:43 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1001,7 +1070,7 @@
         <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>50</v>
@@ -1047,7 +1116,7 @@
         <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>51</v>
@@ -1074,7 +1143,7 @@
         <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>52</v>
@@ -1103,7 +1172,7 @@
         <v>62</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>55</v>
@@ -1156,7 +1225,7 @@
         <v>62</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>53</v>
@@ -1209,7 +1278,7 @@
         <v>62</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>54</v>
@@ -1265,7 +1334,7 @@
         <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="C8" s="23" t="s">
         <v>47</v>
@@ -1297,7 +1366,7 @@
         <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="C9" s="23" t="s">
         <v>48</v>
@@ -1326,7 +1395,7 @@
         <v>62</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="C10" s="23" t="s">
         <v>49</v>
@@ -1355,7 +1424,7 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>77</v>
@@ -1414,7 +1483,7 @@
         <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>78</v>
@@ -1613,7 +1682,7 @@
         <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>56</v>
@@ -1660,7 +1729,7 @@
         <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>27</v>
@@ -1678,7 +1747,7 @@
         <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>26</v>
@@ -1698,7 +1767,7 @@
         <v>62</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>34</v>
@@ -1746,7 +1815,7 @@
         <v>62</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>35</v>
@@ -1776,7 +1845,7 @@
         <v>62</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>37</v>
@@ -1808,7 +1877,7 @@
         <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>28</v>
@@ -1840,7 +1909,7 @@
         <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>29</v>
@@ -1866,7 +1935,7 @@
         <v>62</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>30</v>
@@ -1919,7 +1988,7 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>36</v>
@@ -1954,7 +2023,7 @@
         <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>77</v>
@@ -1989,7 +2058,7 @@
         <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>78</v>

--- a/KatalonData/EmailTextToPay/ManualEntry_Demo.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry_Demo.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="173">
   <si>
     <t>Result</t>
   </si>
@@ -418,6 +418,144 @@
   </si>
   <si>
     <t>Mon Jun 29 14:14:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:27:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:28:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:29:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:30:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:30:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:31:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:32:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:33:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:34:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:35:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:36:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:47:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:47:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:48:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:49:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:50:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:50:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:51:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:52:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:53:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:53:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:54:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 15:55:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:48:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:49:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:50:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:51:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:52:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:53:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:53:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:54:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:55:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:57:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:58:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:11:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:11:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:12:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:13:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:14:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:14:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:15:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:16:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:17:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:17:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:18:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 19:19:00 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -955,7 +1093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AB12"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="6.26953125" collapsed="true"/>
@@ -1066,11 +1204,11 @@
       </c>
     </row>
     <row customFormat="1" customHeight="1" ht="19" r="2" s="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="B2" t="s">
-        <v>104</v>
+      <c r="B2" t="s" s="21">
+        <v>150</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>50</v>
@@ -1112,11 +1250,11 @@
       <c r="AB2" s="9"/>
     </row>
     <row customHeight="1" ht="21.5" r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="B3" t="s">
-        <v>105</v>
+      <c r="B3" t="s" s="21">
+        <v>151</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>51</v>
@@ -1139,11 +1277,11 @@
       </c>
     </row>
     <row ht="25" r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="B4" t="s">
-        <v>106</v>
+      <c r="B4" t="s" s="21">
+        <v>152</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>52</v>
@@ -1168,11 +1306,11 @@
       </c>
     </row>
     <row customHeight="1" ht="38" r="5" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="B5" t="s">
-        <v>107</v>
+      <c r="B5" t="s" s="21">
+        <v>153</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>55</v>
@@ -1221,11 +1359,11 @@
       </c>
     </row>
     <row ht="37.5" r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="B6" t="s">
-        <v>108</v>
+      <c r="B6" t="s" s="21">
+        <v>154</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>53</v>
@@ -1274,11 +1412,11 @@
       </c>
     </row>
     <row ht="37.5" r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="B7" t="s">
-        <v>109</v>
+      <c r="B7" t="s" s="21">
+        <v>155</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>54</v>
@@ -1330,11 +1468,11 @@
       </c>
     </row>
     <row ht="37.5" r="8" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="B8" t="s">
-        <v>110</v>
+      <c r="B8" t="s" s="21">
+        <v>156</v>
       </c>
       <c r="C8" s="23" t="s">
         <v>47</v>
@@ -1362,11 +1500,11 @@
       </c>
     </row>
     <row ht="37.5" r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="B9" t="s">
-        <v>111</v>
+      <c r="B9" t="s" s="21">
+        <v>157</v>
       </c>
       <c r="C9" s="23" t="s">
         <v>48</v>
@@ -1391,11 +1529,11 @@
       </c>
     </row>
     <row ht="37.5" r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="B10" t="s">
-        <v>112</v>
+      <c r="B10" t="s" s="21">
+        <v>158</v>
       </c>
       <c r="C10" s="23" t="s">
         <v>49</v>
@@ -1420,11 +1558,11 @@
       </c>
     </row>
     <row ht="37.5" r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="B11" t="s">
-        <v>113</v>
+      <c r="B11" t="s" s="21">
+        <v>159</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>77</v>
@@ -1479,11 +1617,11 @@
       </c>
     </row>
     <row ht="37.5" r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="B12" t="s">
-        <v>114</v>
+      <c r="B12" t="s" s="21">
+        <v>160</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>78</v>
@@ -1556,7 +1694,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
@@ -1678,11 +1816,11 @@
       </c>
     </row>
     <row ht="37.5" r="2" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="6">
         <v>62</v>
       </c>
-      <c r="B2" t="s">
-        <v>115</v>
+      <c r="B2" t="s" s="6">
+        <v>161</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>56</v>
@@ -1725,11 +1863,11 @@
       </c>
     </row>
     <row ht="13" r="3" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="6">
         <v>62</v>
       </c>
-      <c r="B3" t="s">
-        <v>116</v>
+      <c r="B3" t="s" s="6">
+        <v>162</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>27</v>
@@ -1743,11 +1881,11 @@
       </c>
     </row>
     <row ht="13" r="4" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="6">
         <v>62</v>
       </c>
-      <c r="B4" t="s">
-        <v>117</v>
+      <c r="B4" t="s" s="6">
+        <v>163</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>26</v>
@@ -1763,11 +1901,11 @@
       </c>
     </row>
     <row ht="25" r="5" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="6">
         <v>62</v>
       </c>
-      <c r="B5" t="s">
-        <v>118</v>
+      <c r="B5" t="s" s="6">
+        <v>164</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>34</v>
@@ -1811,11 +1949,11 @@
       </c>
     </row>
     <row ht="25" r="6" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="6">
         <v>62</v>
       </c>
-      <c r="B6" t="s">
-        <v>119</v>
+      <c r="B6" t="s" s="6">
+        <v>165</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>35</v>
@@ -1841,11 +1979,11 @@
       </c>
     </row>
     <row ht="25" r="7" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="6">
         <v>62</v>
       </c>
-      <c r="B7" t="s">
-        <v>120</v>
+      <c r="B7" t="s" s="6">
+        <v>166</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>37</v>
@@ -1873,11 +2011,11 @@
       </c>
     </row>
     <row ht="25" r="8" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="6">
         <v>62</v>
       </c>
-      <c r="B8" t="s">
-        <v>121</v>
+      <c r="B8" t="s" s="6">
+        <v>167</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>28</v>
@@ -1905,11 +2043,11 @@
       </c>
     </row>
     <row ht="25" r="9" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="6">
         <v>62</v>
       </c>
-      <c r="B9" t="s">
-        <v>122</v>
+      <c r="B9" t="s" s="6">
+        <v>168</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>29</v>
@@ -1931,11 +2069,11 @@
       </c>
     </row>
     <row ht="25" r="10" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="6">
         <v>62</v>
       </c>
-      <c r="B10" t="s">
-        <v>123</v>
+      <c r="B10" t="s" s="6">
+        <v>169</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>30</v>
@@ -1984,11 +2122,11 @@
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="6">
         <v>62</v>
       </c>
-      <c r="B11" t="s">
-        <v>124</v>
+      <c r="B11" t="s" s="6">
+        <v>170</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>36</v>
@@ -2019,11 +2157,11 @@
       </c>
     </row>
     <row ht="37.5" r="12" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="6">
         <v>62</v>
       </c>
-      <c r="B12" t="s">
-        <v>125</v>
+      <c r="B12" t="s" s="6">
+        <v>171</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>77</v>
@@ -2054,11 +2192,11 @@
       </c>
     </row>
     <row ht="37.5" r="13" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="6">
         <v>62</v>
       </c>
-      <c r="B13" t="s">
-        <v>126</v>
+      <c r="B13" t="s" s="6">
+        <v>172</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>78</v>
